--- a/output/yearly_population_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_79_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3634</v>
+        <v>7052</v>
       </c>
       <c r="C2" t="n">
-        <v>10464</v>
+        <v>6045</v>
       </c>
       <c r="D2" t="n">
-        <v>20162</v>
+        <v>16418</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2527</v>
+        <v>4111</v>
       </c>
       <c r="C3" t="n">
-        <v>5631</v>
+        <v>4938</v>
       </c>
       <c r="D3" t="n">
-        <v>10823</v>
+        <v>13963</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2313</v>
+        <v>3188</v>
       </c>
       <c r="C4" t="n">
-        <v>3460</v>
+        <v>6357</v>
       </c>
       <c r="D4" t="n">
-        <v>5357</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1455</v>
+        <v>2191</v>
       </c>
       <c r="C5" t="n">
-        <v>3868</v>
+        <v>4695</v>
       </c>
       <c r="D5" t="n">
-        <v>2254</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>1258</v>
       </c>
       <c r="C6" t="n">
-        <v>3541</v>
+        <v>2526</v>
       </c>
       <c r="D6" t="n">
-        <v>1075</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>596</v>
       </c>
       <c r="C7" t="n">
-        <v>2514</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>1229</v>
+        <v>655</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5213</v>
+        <v>8607</v>
       </c>
       <c r="C2" t="n">
-        <v>10535</v>
+        <v>7727</v>
       </c>
       <c r="D2" t="n">
-        <v>23081</v>
+        <v>20063</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2469</v>
+        <v>4435</v>
       </c>
       <c r="C3" t="n">
-        <v>6918</v>
+        <v>4788</v>
       </c>
       <c r="D3" t="n">
-        <v>11365</v>
+        <v>13358</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2066</v>
+        <v>3065</v>
       </c>
       <c r="C4" t="n">
-        <v>4450</v>
+        <v>5543</v>
       </c>
       <c r="D4" t="n">
-        <v>6034</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1628</v>
+        <v>2321</v>
       </c>
       <c r="C5" t="n">
-        <v>3558</v>
+        <v>5318</v>
       </c>
       <c r="D5" t="n">
-        <v>2691</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>984</v>
+        <v>1510</v>
       </c>
       <c r="C6" t="n">
-        <v>3656</v>
+        <v>3479</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>500</v>
+        <v>794</v>
       </c>
       <c r="C7" t="n">
-        <v>2951</v>
+        <v>1811</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>326</v>
       </c>
       <c r="C8" t="n">
-        <v>1795</v>
+        <v>920</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>258</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5942</v>
+        <v>10352</v>
       </c>
       <c r="C2" t="n">
-        <v>19841</v>
+        <v>7430</v>
       </c>
       <c r="D2" t="n">
-        <v>18137</v>
+        <v>25942</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2909</v>
+        <v>4959</v>
       </c>
       <c r="C3" t="n">
-        <v>7463</v>
+        <v>5325</v>
       </c>
       <c r="D3" t="n">
-        <v>12119</v>
+        <v>13468</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1929</v>
+        <v>3081</v>
       </c>
       <c r="C4" t="n">
-        <v>5404</v>
+        <v>5094</v>
       </c>
       <c r="D4" t="n">
-        <v>6669</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1614</v>
+        <v>2338</v>
       </c>
       <c r="C5" t="n">
-        <v>3835</v>
+        <v>5251</v>
       </c>
       <c r="D5" t="n">
-        <v>3064</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1132</v>
+        <v>1692</v>
       </c>
       <c r="C6" t="n">
-        <v>3580</v>
+        <v>4206</v>
       </c>
       <c r="D6" t="n">
-        <v>1424</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>623</v>
+        <v>965</v>
       </c>
       <c r="C7" t="n">
-        <v>3211</v>
+        <v>2462</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>446</v>
       </c>
       <c r="C8" t="n">
-        <v>2258</v>
+        <v>1259</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="C9" t="n">
-        <v>1167</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
         <v>333</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>495</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
         <v>166</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5379</v>
+        <v>9349</v>
       </c>
       <c r="C2" t="n">
-        <v>13333</v>
+        <v>5052</v>
       </c>
       <c r="D2" t="n">
-        <v>14974</v>
+        <v>21270</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3502</v>
+        <v>5793</v>
       </c>
       <c r="C3" t="n">
-        <v>11883</v>
+        <v>8057</v>
       </c>
       <c r="D3" t="n">
-        <v>13153</v>
+        <v>15221</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1491</v>
+        <v>2160</v>
       </c>
       <c r="C4" t="n">
-        <v>6690</v>
+        <v>7877</v>
       </c>
       <c r="D4" t="n">
-        <v>6505</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1045</v>
+        <v>1563</v>
       </c>
       <c r="C5" t="n">
-        <v>3508</v>
+        <v>4121</v>
       </c>
       <c r="D5" t="n">
-        <v>2248</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>575</v>
+        <v>891</v>
       </c>
       <c r="C6" t="n">
-        <v>3146</v>
+        <v>2412</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>2212</v>
+        <v>1233</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>1143</v>
+        <v>622</v>
       </c>
       <c r="D8" t="n">
         <v>326</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>485</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>162</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3197</v>
+        <v>5567</v>
       </c>
       <c r="C2" t="n">
-        <v>7108</v>
+        <v>3239</v>
       </c>
       <c r="D2" t="n">
-        <v>11614</v>
+        <v>15774</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>6274</v>
       </c>
       <c r="C3" t="n">
-        <v>11364</v>
+        <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>12643</v>
+        <v>15166</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1997</v>
+        <v>3107</v>
       </c>
       <c r="C4" t="n">
-        <v>9250</v>
+        <v>8100</v>
       </c>
       <c r="D4" t="n">
-        <v>7453</v>
+        <v>9980</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="n">
-        <v>4916</v>
+        <v>5783</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>1067</v>
       </c>
       <c r="C6" t="n">
-        <v>3432</v>
+        <v>3126</v>
       </c>
       <c r="D6" t="n">
-        <v>906</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>386</v>
       </c>
       <c r="C7" t="n">
-        <v>2662</v>
+        <v>1664</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1477</v>
+        <v>812</v>
       </c>
       <c r="D8" t="n">
         <v>340</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>550</v>
+        <v>371</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2609</v>
+        <v>5983</v>
       </c>
       <c r="C2" t="n">
-        <v>9246</v>
+        <v>4399</v>
       </c>
       <c r="D2" t="n">
-        <v>10780</v>
+        <v>14024</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2929</v>
+        <v>5015</v>
       </c>
       <c r="C3" t="n">
-        <v>8302</v>
+        <v>4133</v>
       </c>
       <c r="D3" t="n">
-        <v>11746</v>
+        <v>14355</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2362</v>
+        <v>3859</v>
       </c>
       <c r="C4" t="n">
-        <v>10092</v>
+        <v>6906</v>
       </c>
       <c r="D4" t="n">
-        <v>8073</v>
+        <v>10427</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1341</v>
+        <v>2038</v>
       </c>
       <c r="C5" t="n">
-        <v>6852</v>
+        <v>6830</v>
       </c>
       <c r="D5" t="n">
-        <v>3392</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>810</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="n">
-        <v>4101</v>
+        <v>4294</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>578</v>
       </c>
       <c r="C7" t="n">
-        <v>2992</v>
+        <v>2324</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>1978</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>914</v>
+        <v>546</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>118</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1546</v>
+        <v>3571</v>
       </c>
       <c r="C2" t="n">
-        <v>4305</v>
+        <v>2031</v>
       </c>
       <c r="D2" t="n">
-        <v>7530</v>
+        <v>9665</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2751</v>
+        <v>5062</v>
       </c>
       <c r="C3" t="n">
-        <v>8366</v>
+        <v>4092</v>
       </c>
       <c r="D3" t="n">
-        <v>11382</v>
+        <v>13973</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2609</v>
+        <v>4262</v>
       </c>
       <c r="C4" t="n">
-        <v>10266</v>
+        <v>6493</v>
       </c>
       <c r="D4" t="n">
-        <v>8564</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>2129</v>
       </c>
       <c r="C5" t="n">
-        <v>8515</v>
+        <v>7898</v>
       </c>
       <c r="D5" t="n">
-        <v>3581</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>678</v>
+        <v>1043</v>
       </c>
       <c r="C6" t="n">
-        <v>5150</v>
+        <v>5119</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>3331</v>
+        <v>2328</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1496</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>115</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2701</v>
+        <v>4333</v>
       </c>
       <c r="C2" t="n">
-        <v>4581</v>
+        <v>4211</v>
       </c>
       <c r="D2" t="n">
-        <v>8621</v>
+        <v>11082</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1936</v>
+        <v>3787</v>
       </c>
       <c r="C3" t="n">
-        <v>5817</v>
+        <v>2792</v>
       </c>
       <c r="D3" t="n">
-        <v>10093</v>
+        <v>12448</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2336</v>
+        <v>4049</v>
       </c>
       <c r="C4" t="n">
-        <v>9158</v>
+        <v>5267</v>
       </c>
       <c r="D4" t="n">
-        <v>8845</v>
+        <v>11177</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1686</v>
+        <v>2644</v>
       </c>
       <c r="C5" t="n">
-        <v>9209</v>
+        <v>7099</v>
       </c>
       <c r="D5" t="n">
-        <v>4189</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>874</v>
+        <v>1323</v>
       </c>
       <c r="C6" t="n">
-        <v>6574</v>
+        <v>6371</v>
       </c>
       <c r="D6" t="n">
-        <v>1460</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>4125</v>
+        <v>3471</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>2190</v>
+        <v>1458</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>727</v>
+        <v>477</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>173</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1776</v>
+        <v>3308</v>
       </c>
       <c r="C2" t="n">
-        <v>2855</v>
+        <v>2937</v>
       </c>
       <c r="D2" t="n">
-        <v>6747</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1910</v>
+        <v>3474</v>
       </c>
       <c r="C3" t="n">
-        <v>4888</v>
+        <v>3077</v>
       </c>
       <c r="D3" t="n">
-        <v>9367</v>
+        <v>11606</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2047</v>
+        <v>3656</v>
       </c>
       <c r="C4" t="n">
-        <v>7884</v>
+        <v>4287</v>
       </c>
       <c r="D4" t="n">
-        <v>8913</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1793</v>
+        <v>2918</v>
       </c>
       <c r="C5" t="n">
-        <v>9264</v>
+        <v>6487</v>
       </c>
       <c r="D5" t="n">
-        <v>4593</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1029</v>
+        <v>1553</v>
       </c>
       <c r="C6" t="n">
-        <v>7660</v>
+        <v>6869</v>
       </c>
       <c r="D6" t="n">
-        <v>1721</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>5006</v>
+        <v>4446</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2721</v>
+        <v>1954</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>835</v>
+        <v>563</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3400,7 +3400,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2648</v>
+        <v>4456</v>
       </c>
       <c r="C2" t="n">
-        <v>6083</v>
+        <v>9621</v>
       </c>
       <c r="D2" t="n">
-        <v>6368</v>
+        <v>13989</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1552</v>
+        <v>2870</v>
       </c>
       <c r="C3" t="n">
-        <v>3632</v>
+        <v>2705</v>
       </c>
       <c r="D3" t="n">
-        <v>8453</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1754</v>
+        <v>3150</v>
       </c>
       <c r="C4" t="n">
-        <v>6454</v>
+        <v>3675</v>
       </c>
       <c r="D4" t="n">
-        <v>8707</v>
+        <v>10847</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1718</v>
+        <v>2892</v>
       </c>
       <c r="C5" t="n">
-        <v>8514</v>
+        <v>5443</v>
       </c>
       <c r="D5" t="n">
-        <v>5033</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1198</v>
+        <v>1881</v>
       </c>
       <c r="C6" t="n">
-        <v>8211</v>
+        <v>6659</v>
       </c>
       <c r="D6" t="n">
-        <v>2057</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>427</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>6041</v>
+        <v>5370</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>3503</v>
+        <v>2875</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1452</v>
+        <v>1031</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>418</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4139</v>
+        <v>7490</v>
       </c>
       <c r="C2" t="n">
-        <v>11067</v>
+        <v>5890</v>
       </c>
       <c r="D2" t="n">
-        <v>10618</v>
+        <v>25916</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1912</v>
+        <v>3157</v>
       </c>
       <c r="C2" t="n">
-        <v>3504</v>
+        <v>5388</v>
       </c>
       <c r="D2" t="n">
-        <v>4737</v>
+        <v>10296</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2102</v>
+        <v>3866</v>
       </c>
       <c r="C3" t="n">
-        <v>4500</v>
+        <v>4594</v>
       </c>
       <c r="D3" t="n">
-        <v>9056</v>
+        <v>11676</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2482</v>
+        <v>4256</v>
       </c>
       <c r="C4" t="n">
-        <v>9241</v>
+        <v>5459</v>
       </c>
       <c r="D4" t="n">
-        <v>8981</v>
+        <v>11257</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1138</v>
+        <v>1844</v>
       </c>
       <c r="C5" t="n">
-        <v>11994</v>
+        <v>8760</v>
       </c>
       <c r="D5" t="n">
-        <v>4631</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>394</v>
+        <v>620</v>
       </c>
       <c r="C6" t="n">
-        <v>7449</v>
+        <v>6633</v>
       </c>
       <c r="D6" t="n">
-        <v>1704</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>3432</v>
+        <v>2817</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1422</v>
+        <v>1010</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>409</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5619</v>
+        <v>8137</v>
       </c>
       <c r="C2" t="n">
-        <v>8186</v>
+        <v>3571</v>
       </c>
       <c r="D2" t="n">
-        <v>12663</v>
+        <v>24141</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1760</v>
+        <v>3181</v>
       </c>
       <c r="C3" t="n">
-        <v>5577</v>
+        <v>2968</v>
       </c>
       <c r="D3" t="n">
-        <v>2423</v>
+        <v>4993</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3657</v>
+        <v>5966</v>
       </c>
       <c r="C2" t="n">
-        <v>8785</v>
+        <v>3552</v>
       </c>
       <c r="D2" t="n">
-        <v>15914</v>
+        <v>24699</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3027</v>
+        <v>4647</v>
       </c>
       <c r="C3" t="n">
-        <v>6082</v>
+        <v>2853</v>
       </c>
       <c r="D3" t="n">
-        <v>3964</v>
+        <v>7842</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>799</v>
+        <v>1416</v>
       </c>
       <c r="C4" t="n">
-        <v>3311</v>
+        <v>1784</v>
       </c>
       <c r="D4" t="n">
-        <v>1669</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3684</v>
+        <v>6436</v>
       </c>
       <c r="C2" t="n">
-        <v>5762</v>
+        <v>5665</v>
       </c>
       <c r="D2" t="n">
-        <v>17191</v>
+        <v>21557</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2748</v>
+        <v>4357</v>
       </c>
       <c r="C3" t="n">
-        <v>6540</v>
+        <v>2798</v>
       </c>
       <c r="D3" t="n">
-        <v>5590</v>
+        <v>9974</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1624</v>
+        <v>2579</v>
       </c>
       <c r="C4" t="n">
-        <v>4811</v>
+        <v>2324</v>
       </c>
       <c r="D4" t="n">
-        <v>2058</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>382</v>
+        <v>629</v>
       </c>
       <c r="C5" t="n">
-        <v>1906</v>
+        <v>1073</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4813</v>
+        <v>6793</v>
       </c>
       <c r="C2" t="n">
-        <v>4723</v>
+        <v>10734</v>
       </c>
       <c r="D2" t="n">
-        <v>15681</v>
+        <v>28296</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2620</v>
+        <v>4424</v>
       </c>
       <c r="C3" t="n">
-        <v>5343</v>
+        <v>3719</v>
       </c>
       <c r="D3" t="n">
-        <v>6959</v>
+        <v>11032</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1838</v>
+        <v>2916</v>
       </c>
       <c r="C4" t="n">
-        <v>5640</v>
+        <v>2530</v>
       </c>
       <c r="D4" t="n">
-        <v>2639</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>820</v>
+        <v>1314</v>
       </c>
       <c r="C5" t="n">
-        <v>3372</v>
+        <v>1699</v>
       </c>
       <c r="D5" t="n">
-        <v>1327</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>234</v>
+        <v>335</v>
       </c>
       <c r="C6" t="n">
-        <v>1097</v>
+        <v>683</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5532,7 +5532,7 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5536</v>
+        <v>7173</v>
       </c>
       <c r="C2" t="n">
-        <v>5257</v>
+        <v>10745</v>
       </c>
       <c r="D2" t="n">
-        <v>17266</v>
+        <v>26545</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2672</v>
+        <v>4052</v>
       </c>
       <c r="C3" t="n">
-        <v>4117</v>
+        <v>5983</v>
       </c>
       <c r="D3" t="n">
-        <v>7333</v>
+        <v>12117</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1385</v>
+        <v>2279</v>
       </c>
       <c r="C4" t="n">
-        <v>4485</v>
+        <v>2609</v>
       </c>
       <c r="D4" t="n">
-        <v>2918</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>686</v>
+        <v>1093</v>
       </c>
       <c r="C5" t="n">
-        <v>3298</v>
+        <v>1554</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>386</v>
       </c>
       <c r="C6" t="n">
-        <v>1511</v>
+        <v>793</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>458</v>
+        <v>330</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>193</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4389</v>
+        <v>5846</v>
       </c>
       <c r="C2" t="n">
-        <v>3128</v>
+        <v>8082</v>
       </c>
       <c r="D2" t="n">
-        <v>21752</v>
+        <v>21099</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3417</v>
+        <v>4698</v>
       </c>
       <c r="C3" t="n">
-        <v>4111</v>
+        <v>7540</v>
       </c>
       <c r="D3" t="n">
-        <v>8462</v>
+        <v>13649</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1784</v>
+        <v>2746</v>
       </c>
       <c r="C4" t="n">
-        <v>4169</v>
+        <v>4595</v>
       </c>
       <c r="D4" t="n">
-        <v>3691</v>
+        <v>6034</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>918</v>
+        <v>1505</v>
       </c>
       <c r="C5" t="n">
-        <v>3892</v>
+        <v>2139</v>
       </c>
       <c r="D5" t="n">
-        <v>1521</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>436</v>
+        <v>680</v>
       </c>
       <c r="C6" t="n">
-        <v>2521</v>
+        <v>1214</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="C7" t="n">
-        <v>1056</v>
+        <v>585</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>198</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2860</v>
+        <v>5781</v>
       </c>
       <c r="C2" t="n">
-        <v>9762</v>
+        <v>4498</v>
       </c>
       <c r="D2" t="n">
-        <v>20160</v>
+        <v>21214</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3205</v>
+        <v>4333</v>
       </c>
       <c r="C3" t="n">
-        <v>3094</v>
+        <v>6782</v>
       </c>
       <c r="D3" t="n">
-        <v>9979</v>
+        <v>13858</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2216</v>
+        <v>3201</v>
       </c>
       <c r="C4" t="n">
-        <v>4049</v>
+        <v>6167</v>
       </c>
       <c r="D4" t="n">
-        <v>4494</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1187</v>
+        <v>1850</v>
       </c>
       <c r="C5" t="n">
-        <v>3925</v>
+        <v>3438</v>
       </c>
       <c r="D5" t="n">
-        <v>1855</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>611</v>
+        <v>991</v>
       </c>
       <c r="C6" t="n">
-        <v>3228</v>
+        <v>1688</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260</v>
+        <v>393</v>
       </c>
       <c r="C7" t="n">
-        <v>1830</v>
+        <v>905</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>710</v>
+        <v>435</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">

--- a/output/yearly_population_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_79_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7052</v>
+        <v>4605</v>
       </c>
       <c r="C2" t="n">
-        <v>6045</v>
+        <v>11152</v>
       </c>
       <c r="D2" t="n">
-        <v>16418</v>
+        <v>26786</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4111</v>
+        <v>3201</v>
       </c>
       <c r="C3" t="n">
-        <v>4938</v>
+        <v>5549</v>
       </c>
       <c r="D3" t="n">
-        <v>13963</v>
+        <v>15124</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3188</v>
+        <v>2357</v>
       </c>
       <c r="C4" t="n">
-        <v>6357</v>
+        <v>6085</v>
       </c>
       <c r="D4" t="n">
-        <v>8150</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2191</v>
+        <v>1565</v>
       </c>
       <c r="C5" t="n">
-        <v>4695</v>
+        <v>4744</v>
       </c>
       <c r="D5" t="n">
-        <v>3505</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1258</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>2526</v>
+        <v>2681</v>
       </c>
       <c r="D6" t="n">
-        <v>1414</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>596</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>1271</v>
+        <v>1475</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>655</v>
+        <v>759</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>76</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8607</v>
+        <v>5927</v>
       </c>
       <c r="C2" t="n">
-        <v>7727</v>
+        <v>7107</v>
       </c>
       <c r="D2" t="n">
-        <v>20063</v>
+        <v>37070</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4435</v>
+        <v>3129</v>
       </c>
       <c r="C3" t="n">
-        <v>4788</v>
+        <v>7124</v>
       </c>
       <c r="D3" t="n">
-        <v>13358</v>
+        <v>15693</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3065</v>
+        <v>2330</v>
       </c>
       <c r="C4" t="n">
-        <v>5543</v>
+        <v>5642</v>
       </c>
       <c r="D4" t="n">
-        <v>8850</v>
+        <v>8488</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2321</v>
+        <v>1705</v>
       </c>
       <c r="C5" t="n">
-        <v>5318</v>
+        <v>5276</v>
       </c>
       <c r="D5" t="n">
-        <v>4078</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1510</v>
+        <v>1094</v>
       </c>
       <c r="C6" t="n">
-        <v>3479</v>
+        <v>3559</v>
       </c>
       <c r="D6" t="n">
-        <v>1716</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>794</v>
+        <v>581</v>
       </c>
       <c r="C7" t="n">
-        <v>1811</v>
+        <v>2018</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="C8" t="n">
-        <v>920</v>
+        <v>1059</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10352</v>
+        <v>7800</v>
       </c>
       <c r="C2" t="n">
-        <v>7430</v>
+        <v>7477</v>
       </c>
       <c r="D2" t="n">
-        <v>25942</v>
+        <v>28365</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4959</v>
+        <v>3454</v>
       </c>
       <c r="C3" t="n">
-        <v>5325</v>
+        <v>6308</v>
       </c>
       <c r="D3" t="n">
-        <v>13468</v>
+        <v>17399</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>2263</v>
       </c>
       <c r="C4" t="n">
-        <v>5094</v>
+        <v>6179</v>
       </c>
       <c r="D4" t="n">
-        <v>9145</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2338</v>
+        <v>1742</v>
       </c>
       <c r="C5" t="n">
-        <v>5251</v>
+        <v>5270</v>
       </c>
       <c r="D5" t="n">
-        <v>4602</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1692</v>
+        <v>1224</v>
       </c>
       <c r="C6" t="n">
-        <v>4206</v>
+        <v>4200</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>965</v>
+        <v>713</v>
       </c>
       <c r="C7" t="n">
-        <v>2462</v>
+        <v>2651</v>
       </c>
       <c r="D7" t="n">
-        <v>909</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>446</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>1259</v>
+        <v>1424</v>
       </c>
       <c r="D8" t="n">
-        <v>508</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>635</v>
+        <v>724</v>
       </c>
       <c r="D9" t="n">
         <v>333</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9349</v>
+        <v>6983</v>
       </c>
       <c r="C2" t="n">
-        <v>5052</v>
+        <v>5084</v>
       </c>
       <c r="D2" t="n">
-        <v>21270</v>
+        <v>23360</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5793</v>
+        <v>4135</v>
       </c>
       <c r="C3" t="n">
-        <v>8057</v>
+        <v>9444</v>
       </c>
       <c r="D3" t="n">
-        <v>15221</v>
+        <v>18813</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2160</v>
+        <v>1609</v>
       </c>
       <c r="C4" t="n">
-        <v>7877</v>
+        <v>8499</v>
       </c>
       <c r="D4" t="n">
-        <v>9150</v>
+        <v>9091</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1563</v>
+        <v>1130</v>
       </c>
       <c r="C5" t="n">
-        <v>4121</v>
+        <v>4116</v>
       </c>
       <c r="D5" t="n">
-        <v>3229</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>891</v>
+        <v>658</v>
       </c>
       <c r="C6" t="n">
-        <v>2412</v>
+        <v>2597</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1233</v>
+        <v>1395</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>709</v>
       </c>
       <c r="D8" t="n">
         <v>326</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5567</v>
+        <v>4073</v>
       </c>
       <c r="C2" t="n">
-        <v>3239</v>
+        <v>2763</v>
       </c>
       <c r="D2" t="n">
-        <v>15774</v>
+        <v>16571</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6274</v>
+        <v>4580</v>
       </c>
       <c r="C3" t="n">
-        <v>6046</v>
+        <v>6738</v>
       </c>
       <c r="D3" t="n">
-        <v>15166</v>
+        <v>18347</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3107</v>
+        <v>2261</v>
       </c>
       <c r="C4" t="n">
-        <v>8100</v>
+        <v>9093</v>
       </c>
       <c r="D4" t="n">
-        <v>9980</v>
+        <v>10482</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>1240</v>
       </c>
       <c r="C5" t="n">
-        <v>5783</v>
+        <v>6037</v>
       </c>
       <c r="D5" t="n">
-        <v>3931</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1067</v>
+        <v>785</v>
       </c>
       <c r="C6" t="n">
-        <v>3126</v>
+        <v>3254</v>
       </c>
       <c r="D6" t="n">
-        <v>1129</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>1664</v>
+        <v>1847</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>812</v>
+        <v>923</v>
       </c>
       <c r="D8" t="n">
         <v>340</v>
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
         <v>258</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5983</v>
+        <v>4000</v>
       </c>
       <c r="C2" t="n">
-        <v>4399</v>
+        <v>11390</v>
       </c>
       <c r="D2" t="n">
-        <v>14024</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5015</v>
+        <v>3664</v>
       </c>
       <c r="C3" t="n">
-        <v>4133</v>
+        <v>4254</v>
       </c>
       <c r="D3" t="n">
-        <v>14355</v>
+        <v>17005</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3859</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>6906</v>
+        <v>7815</v>
       </c>
       <c r="D4" t="n">
-        <v>10427</v>
+        <v>11446</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2038</v>
+        <v>1484</v>
       </c>
       <c r="C5" t="n">
-        <v>6830</v>
+        <v>7348</v>
       </c>
       <c r="D5" t="n">
-        <v>4798</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1226</v>
+        <v>898</v>
       </c>
       <c r="C6" t="n">
-        <v>4294</v>
+        <v>4509</v>
       </c>
       <c r="D6" t="n">
-        <v>1544</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>578</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>2324</v>
+        <v>2452</v>
       </c>
       <c r="D7" t="n">
-        <v>632</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1170</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>546</v>
+        <v>614</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3571</v>
+        <v>2370</v>
       </c>
       <c r="C2" t="n">
-        <v>2031</v>
+        <v>5314</v>
       </c>
       <c r="D2" t="n">
-        <v>9665</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5062</v>
+        <v>3612</v>
       </c>
       <c r="C3" t="n">
-        <v>4092</v>
+        <v>6481</v>
       </c>
       <c r="D3" t="n">
-        <v>13973</v>
+        <v>16293</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4262</v>
+        <v>3107</v>
       </c>
       <c r="C4" t="n">
-        <v>6493</v>
+        <v>7281</v>
       </c>
       <c r="D4" t="n">
-        <v>11033</v>
+        <v>12171</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2129</v>
+        <v>1561</v>
       </c>
       <c r="C5" t="n">
-        <v>7898</v>
+        <v>8502</v>
       </c>
       <c r="D5" t="n">
-        <v>5126</v>
+        <v>4813</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1043</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>5119</v>
+        <v>5390</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2328</v>
+        <v>2507</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>901</v>
+        <v>1012</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4333</v>
+        <v>2566</v>
       </c>
       <c r="C2" t="n">
-        <v>4211</v>
+        <v>9848</v>
       </c>
       <c r="D2" t="n">
-        <v>11082</v>
+        <v>15595</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3787</v>
+        <v>2654</v>
       </c>
       <c r="C3" t="n">
-        <v>2792</v>
+        <v>5298</v>
       </c>
       <c r="D3" t="n">
-        <v>12448</v>
+        <v>14450</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4049</v>
+        <v>2894</v>
       </c>
       <c r="C4" t="n">
-        <v>5267</v>
+        <v>6753</v>
       </c>
       <c r="D4" t="n">
-        <v>11177</v>
+        <v>12434</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2644</v>
+        <v>1933</v>
       </c>
       <c r="C5" t="n">
-        <v>7099</v>
+        <v>7855</v>
       </c>
       <c r="D5" t="n">
-        <v>5926</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1323</v>
+        <v>974</v>
       </c>
       <c r="C6" t="n">
-        <v>6371</v>
+        <v>6707</v>
       </c>
       <c r="D6" t="n">
-        <v>1963</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>3471</v>
+        <v>3713</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1458</v>
+        <v>1573</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>477</v>
+        <v>531</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3308</v>
+        <v>1863</v>
       </c>
       <c r="C2" t="n">
-        <v>2937</v>
+        <v>5627</v>
       </c>
       <c r="D2" t="n">
-        <v>8339</v>
+        <v>11964</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3474</v>
+        <v>2301</v>
       </c>
       <c r="C3" t="n">
-        <v>3077</v>
+        <v>6495</v>
       </c>
       <c r="D3" t="n">
-        <v>11606</v>
+        <v>13801</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3656</v>
+        <v>2601</v>
       </c>
       <c r="C4" t="n">
-        <v>4287</v>
+        <v>6220</v>
       </c>
       <c r="D4" t="n">
-        <v>11115</v>
+        <v>12565</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2918</v>
+        <v>2096</v>
       </c>
       <c r="C5" t="n">
-        <v>6487</v>
+        <v>7526</v>
       </c>
       <c r="D5" t="n">
-        <v>6464</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1553</v>
+        <v>1153</v>
       </c>
       <c r="C6" t="n">
-        <v>6869</v>
+        <v>7342</v>
       </c>
       <c r="D6" t="n">
-        <v>2320</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>4446</v>
+        <v>4699</v>
       </c>
       <c r="D7" t="n">
-        <v>834</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1954</v>
+        <v>2072</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>563</v>
+        <v>618</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4456</v>
+        <v>2674</v>
       </c>
       <c r="C2" t="n">
-        <v>9621</v>
+        <v>4666</v>
       </c>
       <c r="D2" t="n">
-        <v>13989</v>
+        <v>24102</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2870</v>
+        <v>1806</v>
       </c>
       <c r="C3" t="n">
-        <v>2705</v>
+        <v>5472</v>
       </c>
       <c r="D3" t="n">
-        <v>10471</v>
+        <v>12697</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3150</v>
+        <v>2190</v>
       </c>
       <c r="C4" t="n">
-        <v>3675</v>
+        <v>6206</v>
       </c>
       <c r="D4" t="n">
-        <v>10847</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2892</v>
+        <v>2067</v>
       </c>
       <c r="C5" t="n">
-        <v>5443</v>
+        <v>6842</v>
       </c>
       <c r="D5" t="n">
-        <v>6830</v>
+        <v>6963</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1881</v>
+        <v>1367</v>
       </c>
       <c r="C6" t="n">
-        <v>6659</v>
+        <v>7350</v>
       </c>
       <c r="D6" t="n">
-        <v>2846</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>5370</v>
+        <v>5727</v>
       </c>
       <c r="D7" t="n">
-        <v>1014</v>
+        <v>924</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>2875</v>
+        <v>2972</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>1094</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7490</v>
+        <v>4889</v>
       </c>
       <c r="C2" t="n">
-        <v>5890</v>
+        <v>6792</v>
       </c>
       <c r="D2" t="n">
-        <v>25916</v>
+        <v>12340</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3157</v>
+        <v>1934</v>
       </c>
       <c r="C2" t="n">
-        <v>5388</v>
+        <v>2687</v>
       </c>
       <c r="D2" t="n">
-        <v>10296</v>
+        <v>17932</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3866</v>
+        <v>2461</v>
       </c>
       <c r="C3" t="n">
-        <v>4594</v>
+        <v>5772</v>
       </c>
       <c r="D3" t="n">
-        <v>11676</v>
+        <v>14369</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4256</v>
+        <v>3028</v>
       </c>
       <c r="C4" t="n">
-        <v>5459</v>
+        <v>8650</v>
       </c>
       <c r="D4" t="n">
-        <v>11257</v>
+        <v>12707</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1844</v>
+        <v>1301</v>
       </c>
       <c r="C5" t="n">
-        <v>8760</v>
+        <v>10235</v>
       </c>
       <c r="D5" t="n">
-        <v>6377</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>442</v>
       </c>
       <c r="C6" t="n">
-        <v>6633</v>
+        <v>6981</v>
       </c>
       <c r="D6" t="n">
-        <v>2259</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>2817</v>
+        <v>2912</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>1072</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8137</v>
+        <v>6177</v>
       </c>
       <c r="C2" t="n">
-        <v>3571</v>
+        <v>4118</v>
       </c>
       <c r="D2" t="n">
-        <v>24141</v>
+        <v>23030</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3181</v>
+        <v>2078</v>
       </c>
       <c r="C3" t="n">
-        <v>2968</v>
+        <v>3423</v>
       </c>
       <c r="D3" t="n">
-        <v>4993</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5966</v>
+        <v>4638</v>
       </c>
       <c r="C2" t="n">
-        <v>3552</v>
+        <v>4414</v>
       </c>
       <c r="D2" t="n">
-        <v>24699</v>
+        <v>19781</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4647</v>
+        <v>3387</v>
       </c>
       <c r="C3" t="n">
-        <v>2853</v>
+        <v>3291</v>
       </c>
       <c r="D3" t="n">
-        <v>7842</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1416</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>1784</v>
+        <v>2050</v>
       </c>
       <c r="D4" t="n">
-        <v>2187</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6436</v>
+        <v>4288</v>
       </c>
       <c r="C2" t="n">
-        <v>5665</v>
+        <v>4892</v>
       </c>
       <c r="D2" t="n">
-        <v>21557</v>
+        <v>22812</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4357</v>
+        <v>3289</v>
       </c>
       <c r="C3" t="n">
-        <v>2798</v>
+        <v>3378</v>
       </c>
       <c r="D3" t="n">
-        <v>9974</v>
+        <v>7715</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2579</v>
+        <v>1829</v>
       </c>
       <c r="C4" t="n">
-        <v>2324</v>
+        <v>2710</v>
       </c>
       <c r="D4" t="n">
-        <v>3206</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>629</v>
+        <v>445</v>
       </c>
       <c r="C5" t="n">
-        <v>1073</v>
+        <v>1216</v>
       </c>
       <c r="D5" t="n">
-        <v>1330</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6793</v>
+        <v>4639</v>
       </c>
       <c r="C2" t="n">
-        <v>10734</v>
+        <v>10420</v>
       </c>
       <c r="D2" t="n">
-        <v>28296</v>
+        <v>26601</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4424</v>
+        <v>3097</v>
       </c>
       <c r="C3" t="n">
-        <v>3719</v>
+        <v>3618</v>
       </c>
       <c r="D3" t="n">
-        <v>11032</v>
+        <v>9466</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2916</v>
+        <v>2174</v>
       </c>
       <c r="C4" t="n">
-        <v>2530</v>
+        <v>2986</v>
       </c>
       <c r="D4" t="n">
-        <v>4343</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1314</v>
+        <v>931</v>
       </c>
       <c r="C5" t="n">
-        <v>1699</v>
+        <v>1979</v>
       </c>
       <c r="D5" t="n">
-        <v>1600</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>335</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>683</v>
+        <v>762</v>
       </c>
       <c r="D6" t="n">
-        <v>968</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7173</v>
+        <v>5420</v>
       </c>
       <c r="C2" t="n">
-        <v>10745</v>
+        <v>10919</v>
       </c>
       <c r="D2" t="n">
-        <v>26545</v>
+        <v>23385</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4052</v>
+        <v>2833</v>
       </c>
       <c r="C3" t="n">
-        <v>5983</v>
+        <v>5811</v>
       </c>
       <c r="D3" t="n">
-        <v>12117</v>
+        <v>10729</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2279</v>
+        <v>1626</v>
       </c>
       <c r="C4" t="n">
-        <v>2609</v>
+        <v>2708</v>
       </c>
       <c r="D4" t="n">
-        <v>4736</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1093</v>
+        <v>807</v>
       </c>
       <c r="C5" t="n">
-        <v>1554</v>
+        <v>1834</v>
       </c>
       <c r="D5" t="n">
-        <v>1627</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>386</v>
+        <v>284</v>
       </c>
       <c r="C6" t="n">
-        <v>793</v>
+        <v>921</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5846</v>
+        <v>4327</v>
       </c>
       <c r="C2" t="n">
-        <v>8082</v>
+        <v>6963</v>
       </c>
       <c r="D2" t="n">
-        <v>21099</v>
+        <v>31549</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4698</v>
+        <v>3432</v>
       </c>
       <c r="C3" t="n">
-        <v>7540</v>
+        <v>7598</v>
       </c>
       <c r="D3" t="n">
-        <v>13649</v>
+        <v>12149</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2746</v>
+        <v>1944</v>
       </c>
       <c r="C4" t="n">
-        <v>4595</v>
+        <v>4558</v>
       </c>
       <c r="D4" t="n">
-        <v>6034</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1505</v>
+        <v>1093</v>
       </c>
       <c r="C5" t="n">
-        <v>2139</v>
+        <v>2316</v>
       </c>
       <c r="D5" t="n">
-        <v>2204</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>680</v>
+        <v>509</v>
       </c>
       <c r="C6" t="n">
-        <v>1214</v>
+        <v>1435</v>
       </c>
       <c r="D6" t="n">
-        <v>962</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>585</v>
+        <v>676</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5781</v>
+        <v>4671</v>
       </c>
       <c r="C2" t="n">
-        <v>4498</v>
+        <v>6450</v>
       </c>
       <c r="D2" t="n">
-        <v>21214</v>
+        <v>25948</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4333</v>
+        <v>3222</v>
       </c>
       <c r="C3" t="n">
-        <v>6782</v>
+        <v>6277</v>
       </c>
       <c r="D3" t="n">
-        <v>13858</v>
+        <v>14378</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3201</v>
+        <v>2294</v>
       </c>
       <c r="C4" t="n">
-        <v>6167</v>
+        <v>6141</v>
       </c>
       <c r="D4" t="n">
-        <v>7312</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1850</v>
+        <v>1340</v>
       </c>
       <c r="C5" t="n">
-        <v>3438</v>
+        <v>3516</v>
       </c>
       <c r="D5" t="n">
-        <v>2814</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>723</v>
       </c>
       <c r="C6" t="n">
-        <v>1688</v>
+        <v>1891</v>
       </c>
       <c r="D6" t="n">
-        <v>1175</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>905</v>
+        <v>1077</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>435</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_79_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4605</v>
+        <v>1105</v>
       </c>
       <c r="C2" t="n">
-        <v>11152</v>
+        <v>1517</v>
       </c>
       <c r="D2" t="n">
-        <v>26786</v>
+        <v>14586</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3201</v>
+        <v>1759</v>
       </c>
       <c r="C3" t="n">
-        <v>5549</v>
+        <v>3484</v>
       </c>
       <c r="D3" t="n">
-        <v>15124</v>
+        <v>12763</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2357</v>
+        <v>1238</v>
       </c>
       <c r="C4" t="n">
-        <v>6085</v>
+        <v>6033</v>
       </c>
       <c r="D4" t="n">
-        <v>7555</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1565</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>4744</v>
+        <v>4563</v>
       </c>
       <c r="D5" t="n">
-        <v>3006</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>2681</v>
+        <v>2021</v>
       </c>
       <c r="D6" t="n">
-        <v>1246</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>1475</v>
+        <v>734</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>759</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5927</v>
+        <v>1550</v>
       </c>
       <c r="C2" t="n">
-        <v>7107</v>
+        <v>6687</v>
       </c>
       <c r="D2" t="n">
-        <v>37070</v>
+        <v>19149</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3129</v>
+        <v>1212</v>
       </c>
       <c r="C3" t="n">
-        <v>7124</v>
+        <v>2120</v>
       </c>
       <c r="D3" t="n">
-        <v>15693</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2330</v>
+        <v>1299</v>
       </c>
       <c r="C4" t="n">
-        <v>5642</v>
+        <v>4488</v>
       </c>
       <c r="D4" t="n">
-        <v>8488</v>
+        <v>6576</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1705</v>
+        <v>811</v>
       </c>
       <c r="C5" t="n">
-        <v>5276</v>
+        <v>5302</v>
       </c>
       <c r="D5" t="n">
-        <v>3657</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>3559</v>
+        <v>3311</v>
       </c>
       <c r="D6" t="n">
-        <v>1487</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>581</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>2018</v>
+        <v>1371</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1059</v>
+        <v>530</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
         <v>323</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7800</v>
+        <v>797</v>
       </c>
       <c r="C2" t="n">
-        <v>7477</v>
+        <v>2682</v>
       </c>
       <c r="D2" t="n">
-        <v>28365</v>
+        <v>12889</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3454</v>
+        <v>1262</v>
       </c>
       <c r="C3" t="n">
-        <v>6308</v>
+        <v>3855</v>
       </c>
       <c r="D3" t="n">
-        <v>17399</v>
+        <v>12702</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2263</v>
+        <v>1428</v>
       </c>
       <c r="C4" t="n">
-        <v>6179</v>
+        <v>3870</v>
       </c>
       <c r="D4" t="n">
-        <v>9336</v>
+        <v>7332</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1742</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>5270</v>
+        <v>5720</v>
       </c>
       <c r="D5" t="n">
-        <v>4206</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1224</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>4200</v>
+        <v>4255</v>
       </c>
       <c r="D6" t="n">
-        <v>1779</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>713</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2651</v>
+        <v>1316</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1424</v>
+        <v>512</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6983</v>
+        <v>464</v>
       </c>
       <c r="C2" t="n">
-        <v>5084</v>
+        <v>4982</v>
       </c>
       <c r="D2" t="n">
-        <v>23360</v>
+        <v>12684</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4135</v>
+        <v>880</v>
       </c>
       <c r="C3" t="n">
-        <v>9444</v>
+        <v>2835</v>
       </c>
       <c r="D3" t="n">
-        <v>18813</v>
+        <v>11939</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1609</v>
+        <v>1200</v>
       </c>
       <c r="C4" t="n">
-        <v>8499</v>
+        <v>3818</v>
       </c>
       <c r="D4" t="n">
-        <v>9091</v>
+        <v>8088</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1130</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>4116</v>
+        <v>4696</v>
       </c>
       <c r="D5" t="n">
-        <v>2873</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>658</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>2597</v>
+        <v>5010</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1395</v>
+        <v>2694</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>709</v>
+        <v>860</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4073</v>
+        <v>394</v>
       </c>
       <c r="C2" t="n">
-        <v>2763</v>
+        <v>3195</v>
       </c>
       <c r="D2" t="n">
-        <v>16571</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4580</v>
+        <v>628</v>
       </c>
       <c r="C3" t="n">
-        <v>6738</v>
+        <v>3445</v>
       </c>
       <c r="D3" t="n">
-        <v>18347</v>
+        <v>11454</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2261</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="n">
-        <v>9093</v>
+        <v>3367</v>
       </c>
       <c r="D4" t="n">
-        <v>10482</v>
+        <v>8511</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1240</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="n">
-        <v>6037</v>
+        <v>4390</v>
       </c>
       <c r="D5" t="n">
-        <v>3616</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>581</v>
       </c>
       <c r="C6" t="n">
-        <v>3254</v>
+        <v>5141</v>
       </c>
       <c r="D6" t="n">
-        <v>1033</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1847</v>
+        <v>3604</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>923</v>
+        <v>1357</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>474</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>698</v>
       </c>
       <c r="C2" t="n">
-        <v>11390</v>
+        <v>7904</v>
       </c>
       <c r="D2" t="n">
-        <v>13830</v>
+        <v>10515</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3664</v>
+        <v>443</v>
       </c>
       <c r="C3" t="n">
-        <v>4254</v>
+        <v>2909</v>
       </c>
       <c r="D3" t="n">
-        <v>17005</v>
+        <v>10375</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>742</v>
       </c>
       <c r="C4" t="n">
-        <v>7815</v>
+        <v>3336</v>
       </c>
       <c r="D4" t="n">
-        <v>11446</v>
+        <v>8760</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1484</v>
+        <v>934</v>
       </c>
       <c r="C5" t="n">
-        <v>7348</v>
+        <v>3839</v>
       </c>
       <c r="D5" t="n">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>4509</v>
+        <v>4743</v>
       </c>
       <c r="D6" t="n">
-        <v>1391</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>2452</v>
+        <v>4330</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1311</v>
+        <v>2316</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>614</v>
+        <v>824</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2370</v>
+        <v>457</v>
       </c>
       <c r="C2" t="n">
-        <v>5314</v>
+        <v>3983</v>
       </c>
       <c r="D2" t="n">
-        <v>9646</v>
+        <v>7486</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3612</v>
+        <v>673</v>
       </c>
       <c r="C3" t="n">
-        <v>6481</v>
+        <v>4601</v>
       </c>
       <c r="D3" t="n">
-        <v>16293</v>
+        <v>11122</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3107</v>
+        <v>1221</v>
       </c>
       <c r="C4" t="n">
-        <v>7281</v>
+        <v>4617</v>
       </c>
       <c r="D4" t="n">
-        <v>12171</v>
+        <v>9152</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1561</v>
+        <v>735</v>
       </c>
       <c r="C5" t="n">
-        <v>8502</v>
+        <v>6147</v>
       </c>
       <c r="D5" t="n">
-        <v>4813</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>5390</v>
+        <v>5544</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2507</v>
+        <v>2269</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1012</v>
+        <v>807</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2566</v>
+        <v>259</v>
       </c>
       <c r="C2" t="n">
-        <v>9848</v>
+        <v>2122</v>
       </c>
       <c r="D2" t="n">
-        <v>15595</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2654</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>5298</v>
+        <v>3762</v>
       </c>
       <c r="D3" t="n">
-        <v>14450</v>
+        <v>9756</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2894</v>
+        <v>804</v>
       </c>
       <c r="C4" t="n">
-        <v>6753</v>
+        <v>4379</v>
       </c>
       <c r="D4" t="n">
-        <v>12434</v>
+        <v>8857</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1933</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>7855</v>
+        <v>4748</v>
       </c>
       <c r="D5" t="n">
-        <v>5726</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>974</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>6707</v>
+        <v>4861</v>
       </c>
       <c r="D6" t="n">
-        <v>1804</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3713</v>
+        <v>2737</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1573</v>
+        <v>927</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1863</v>
+        <v>657</v>
       </c>
       <c r="C2" t="n">
-        <v>5627</v>
+        <v>6762</v>
       </c>
       <c r="D2" t="n">
-        <v>11964</v>
+        <v>10072</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2301</v>
+        <v>313</v>
       </c>
       <c r="C3" t="n">
-        <v>6495</v>
+        <v>2444</v>
       </c>
       <c r="D3" t="n">
-        <v>13801</v>
+        <v>8534</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2601</v>
+        <v>570</v>
       </c>
       <c r="C4" t="n">
-        <v>6220</v>
+        <v>3968</v>
       </c>
       <c r="D4" t="n">
-        <v>12565</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2096</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>7526</v>
+        <v>4443</v>
       </c>
       <c r="D5" t="n">
-        <v>6315</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1153</v>
+        <v>427</v>
       </c>
       <c r="C6" t="n">
-        <v>7342</v>
+        <v>4791</v>
       </c>
       <c r="D6" t="n">
-        <v>2174</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>4699</v>
+        <v>3865</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>2072</v>
+        <v>1822</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2674</v>
+        <v>725</v>
       </c>
       <c r="C2" t="n">
-        <v>4666</v>
+        <v>5722</v>
       </c>
       <c r="D2" t="n">
-        <v>24102</v>
+        <v>9672</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1806</v>
+        <v>388</v>
       </c>
       <c r="C3" t="n">
-        <v>5472</v>
+        <v>4061</v>
       </c>
       <c r="D3" t="n">
-        <v>12697</v>
+        <v>8166</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2190</v>
+        <v>392</v>
       </c>
       <c r="C4" t="n">
-        <v>6206</v>
+        <v>3066</v>
       </c>
       <c r="D4" t="n">
-        <v>12361</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2067</v>
+        <v>574</v>
       </c>
       <c r="C5" t="n">
-        <v>6842</v>
+        <v>4104</v>
       </c>
       <c r="D5" t="n">
-        <v>6963</v>
+        <v>5641</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1367</v>
+        <v>500</v>
       </c>
       <c r="C6" t="n">
-        <v>7350</v>
+        <v>4565</v>
       </c>
       <c r="D6" t="n">
-        <v>2662</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>5727</v>
+        <v>4317</v>
       </c>
       <c r="D7" t="n">
-        <v>924</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>2972</v>
+        <v>2782</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1094</v>
+        <v>1146</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4889</v>
+        <v>2867</v>
       </c>
       <c r="C2" t="n">
-        <v>6792</v>
+        <v>10005</v>
       </c>
       <c r="D2" t="n">
-        <v>12340</v>
+        <v>8012</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1934</v>
+        <v>556</v>
       </c>
       <c r="C2" t="n">
-        <v>2687</v>
+        <v>12753</v>
       </c>
       <c r="D2" t="n">
-        <v>17932</v>
+        <v>13242</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2461</v>
+        <v>437</v>
       </c>
       <c r="C3" t="n">
-        <v>5772</v>
+        <v>4244</v>
       </c>
       <c r="D3" t="n">
-        <v>14369</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3028</v>
+        <v>339</v>
       </c>
       <c r="C4" t="n">
-        <v>8650</v>
+        <v>3459</v>
       </c>
       <c r="D4" t="n">
-        <v>12707</v>
+        <v>8013</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1301</v>
+        <v>455</v>
       </c>
       <c r="C5" t="n">
-        <v>10235</v>
+        <v>3520</v>
       </c>
       <c r="D5" t="n">
-        <v>6317</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>6981</v>
+        <v>4306</v>
       </c>
       <c r="D6" t="n">
-        <v>2092</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>2912</v>
+        <v>4427</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>1072</v>
+        <v>3415</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>1834</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>684</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6177</v>
+        <v>4504</v>
       </c>
       <c r="C2" t="n">
-        <v>4118</v>
+        <v>9641</v>
       </c>
       <c r="D2" t="n">
-        <v>23030</v>
+        <v>15496</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2078</v>
+        <v>949</v>
       </c>
       <c r="C3" t="n">
-        <v>3423</v>
+        <v>3951</v>
       </c>
       <c r="D3" t="n">
-        <v>2712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4638</v>
+        <v>3217</v>
       </c>
       <c r="C2" t="n">
-        <v>4414</v>
+        <v>5235</v>
       </c>
       <c r="D2" t="n">
-        <v>19781</v>
+        <v>17173</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3387</v>
+        <v>2317</v>
       </c>
       <c r="C3" t="n">
-        <v>3291</v>
+        <v>6340</v>
       </c>
       <c r="D3" t="n">
-        <v>5925</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>937</v>
+        <v>466</v>
       </c>
       <c r="C4" t="n">
-        <v>2050</v>
+        <v>2513</v>
       </c>
       <c r="D4" t="n">
-        <v>1727</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4288</v>
+        <v>2323</v>
       </c>
       <c r="C2" t="n">
-        <v>4892</v>
+        <v>4062</v>
       </c>
       <c r="D2" t="n">
-        <v>22812</v>
+        <v>16129</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3289</v>
+        <v>2285</v>
       </c>
       <c r="C3" t="n">
-        <v>3378</v>
+        <v>4951</v>
       </c>
       <c r="D3" t="n">
-        <v>7715</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1829</v>
+        <v>1225</v>
       </c>
       <c r="C4" t="n">
-        <v>2710</v>
+        <v>4738</v>
       </c>
       <c r="D4" t="n">
-        <v>2480</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>445</v>
+        <v>245</v>
       </c>
       <c r="C5" t="n">
-        <v>1216</v>
+        <v>1530</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4639</v>
+        <v>1627</v>
       </c>
       <c r="C2" t="n">
-        <v>10420</v>
+        <v>4954</v>
       </c>
       <c r="D2" t="n">
-        <v>26601</v>
+        <v>20239</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3097</v>
+        <v>1902</v>
       </c>
       <c r="C3" t="n">
-        <v>3618</v>
+        <v>3850</v>
       </c>
       <c r="D3" t="n">
-        <v>9466</v>
+        <v>7131</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2174</v>
+        <v>1516</v>
       </c>
       <c r="C4" t="n">
-        <v>2986</v>
+        <v>4762</v>
       </c>
       <c r="D4" t="n">
-        <v>3335</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>931</v>
+        <v>623</v>
       </c>
       <c r="C5" t="n">
-        <v>1979</v>
+        <v>3284</v>
       </c>
       <c r="D5" t="n">
-        <v>1433</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="C6" t="n">
-        <v>762</v>
+        <v>940</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5420</v>
+        <v>1798</v>
       </c>
       <c r="C2" t="n">
-        <v>10919</v>
+        <v>4772</v>
       </c>
       <c r="D2" t="n">
-        <v>23385</v>
+        <v>28971</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2833</v>
+        <v>1470</v>
       </c>
       <c r="C3" t="n">
-        <v>5811</v>
+        <v>3848</v>
       </c>
       <c r="D3" t="n">
-        <v>10729</v>
+        <v>8621</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1626</v>
+        <v>1459</v>
       </c>
       <c r="C4" t="n">
-        <v>2708</v>
+        <v>4163</v>
       </c>
       <c r="D4" t="n">
-        <v>3769</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>807</v>
+        <v>916</v>
       </c>
       <c r="C5" t="n">
-        <v>1834</v>
+        <v>3996</v>
       </c>
       <c r="D5" t="n">
-        <v>1407</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="C6" t="n">
-        <v>921</v>
+        <v>2122</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>616</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4327</v>
+        <v>2218</v>
       </c>
       <c r="C2" t="n">
-        <v>6963</v>
+        <v>3682</v>
       </c>
       <c r="D2" t="n">
-        <v>31549</v>
+        <v>27141</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3432</v>
+        <v>1348</v>
       </c>
       <c r="C3" t="n">
-        <v>7598</v>
+        <v>3759</v>
       </c>
       <c r="D3" t="n">
-        <v>12149</v>
+        <v>10958</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1944</v>
+        <v>1259</v>
       </c>
       <c r="C4" t="n">
-        <v>4558</v>
+        <v>3876</v>
       </c>
       <c r="D4" t="n">
-        <v>5124</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1093</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="n">
-        <v>2316</v>
+        <v>3996</v>
       </c>
       <c r="D5" t="n">
-        <v>1840</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>1435</v>
+        <v>2999</v>
       </c>
       <c r="D6" t="n">
-        <v>887</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>676</v>
+        <v>1324</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>438</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4671</v>
+        <v>1981</v>
       </c>
       <c r="C2" t="n">
-        <v>6450</v>
+        <v>2238</v>
       </c>
       <c r="D2" t="n">
-        <v>25948</v>
+        <v>21271</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3222</v>
+        <v>2014</v>
       </c>
       <c r="C3" t="n">
-        <v>6277</v>
+        <v>5580</v>
       </c>
       <c r="D3" t="n">
-        <v>14378</v>
+        <v>12106</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2294</v>
+        <v>954</v>
       </c>
       <c r="C4" t="n">
-        <v>6141</v>
+        <v>6291</v>
       </c>
       <c r="D4" t="n">
-        <v>6267</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1340</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>3516</v>
+        <v>2939</v>
       </c>
       <c r="D5" t="n">
-        <v>2414</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>723</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>1891</v>
+        <v>1297</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1077</v>
+        <v>429</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>486</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
